--- a/Ai log/AI_AuditLog_Nghia.xlsx
+++ b/Ai log/AI_AuditLog_Nghia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daomi\.gemini\antigravity\scratch\MSPM-main\Ai log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFAC3BA-DF71-487C-9FEC-FAF36D7329D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{707285E2-C9E8-46C4-AB7D-15C4AA8B7C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="363">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -74,9 +74,6 @@
     <t>Total Prompts Used (all AI tools):</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>Core Prompts Logged:</t>
   </si>
   <si>
@@ -116,21 +113,12 @@
     <t>Thiết kế kiến trúc thuật toán (Merge Sort, Binary Search)</t>
   </si>
   <si>
-    <t>High (60%)</t>
-  </si>
-  <si>
-    <t>Tối ưu độ phức tạp thời gian</t>
-  </si>
-  <si>
     <t>ChatGPT</t>
   </si>
   <si>
     <t>Giải thích khái niệm cơ bản, sửa lỗi vặt</t>
   </si>
   <si>
-    <t>Medium (25%)</t>
-  </si>
-  <si>
     <t>Tra cứu nhanh, fix bug</t>
   </si>
   <si>
@@ -138,9 +126,6 @@
   </si>
   <si>
     <t>Auto-complete các dòng code lặp đi lặp lại</t>
-  </si>
-  <si>
-    <t>Low (15%)</t>
   </si>
   <si>
     <t>Tăng tốc độ gõ code</t>
@@ -909,6 +894,246 @@
   </si>
   <si>
     <t>AI khẳng định dùng playlist.get(mid) trực tiếp trên CDLL vẫn đạt độ phức tạp $O(\log N)$ (Sai).</t>
+  </si>
+  <si>
+    <t>Explanation</t>
+  </si>
+  <si>
+    <t>Algorithm</t>
+  </si>
+  <si>
+    <t>Không hiểu Merge Sort hoạt động</t>
+  </si>
+  <si>
+    <t>Giải thích Merge Sort</t>
+  </si>
+  <si>
+    <t>AI giải thích Divide &amp; Conquer, chia mảng rồi merge và độ phức tạp O(n log n).</t>
+  </si>
+  <si>
+    <t>Hiểu rõ nguyên lý Merge Sort để chuẩn bị báo cáo.</t>
+  </si>
+  <si>
+    <t>Chat log</t>
+  </si>
+  <si>
+    <t>Verification</t>
+  </si>
+  <si>
+    <t>Kiểm tra danh sách bài hát đã sắp xếp chưa</t>
+  </si>
+  <si>
+    <t>Các bài hát này đã được sắp xếp A→Z chưa?</t>
+  </si>
+  <si>
+    <t>AI xác định danh sách chưa được sắp xếp theo tiêu đề và đưa ra thứ tự đúng.</t>
+  </si>
+  <si>
+    <t>Xác nhận dữ liệu hiển thị sai so với mong muốn.</t>
+  </si>
+  <si>
+    <t>Code Review</t>
+  </si>
+  <si>
+    <t>PlaylistSorter</t>
+  </si>
+  <si>
+    <t>Kiểm tra thuật toán Merge Sort</t>
+  </si>
+  <si>
+    <t>Kiểm tra class PlaylistSorter</t>
+  </si>
+  <si>
+    <t>AI đánh giá thuật toán Merge Sort đúng, compare() đúng, stable sort.</t>
+  </si>
+  <si>
+    <t>Giữ nguyên PlaylistSorter, tiếp tục tìm lỗi nơi khác.</t>
+  </si>
+  <si>
+    <t>PlaylistSorter.java</t>
+  </si>
+  <si>
+    <t>Debugging</t>
+  </si>
+  <si>
+    <t>MainServer</t>
+  </si>
+  <si>
+    <t>Sửa MainServer để có sort</t>
+  </si>
+  <si>
+    <t>Đã thêm code nhưng giao diện vẫn chưa thay đổi.</t>
+  </si>
+  <si>
+    <t>MainServer.java</t>
+  </si>
+  <si>
+    <t>Frontend/API</t>
+  </si>
+  <si>
+    <t>Nghi ngờ HTML hoặc JavaScript</t>
+  </si>
+  <si>
+    <t>Có cần sửa HTML không?</t>
+  </si>
+  <si>
+    <t>Xác định frontend chưa phải nguyên nhân.</t>
+  </si>
+  <si>
+    <t>api.js</t>
+  </si>
+  <si>
+    <t>Runtime</t>
+  </si>
+  <si>
+    <t>Server báo Address already in use</t>
+  </si>
+  <si>
+    <t>Server không chạy được</t>
+  </si>
+  <si>
+    <t>Dừng tiến trình Java cũ rồi chạy lại thành công.</t>
+  </si>
+  <si>
+    <t>Terminal log</t>
+  </si>
+  <si>
+    <t>Investigation</t>
+  </si>
+  <si>
+    <t>Không thấy Merge Sort hoạt động</t>
+  </si>
+  <si>
+    <t>Đã chạy lại server nhưng không sort</t>
+  </si>
+  <si>
+    <t>Phát hiện chưa có log, tiếp tục kiểm tra endpoint.</t>
+  </si>
+  <si>
+    <t>Analysis</t>
+  </si>
+  <si>
+    <t>API Flow</t>
+  </si>
+  <si>
+    <t>Không rõ frontend gọi endpoint nào</t>
+  </si>
+  <si>
+    <t>Xác định cần kiểm tra luồng gọi API.</t>
+  </si>
+  <si>
+    <t>Reflection</t>
+  </si>
+  <si>
+    <t>Xác định nguyên nhân không phải Merge Sort</t>
+  </si>
+  <si>
+    <t>Vì sao vẫn chưa sort?</t>
+  </si>
+  <si>
+    <t>AI kết luận Merge Sort đúng, nghi ngờ MainServer hoặc endpoint.</t>
+  </si>
+  <si>
+    <t>Chuyển hướng kiểm tra luồng xử lý thay vì sửa thuật toán.</t>
+  </si>
+  <si>
+    <t>Technical Support</t>
+  </si>
+  <si>
+    <t>VS Code chạy nhiều server</t>
+  </si>
+  <si>
+    <t>Server chạy nhưng không cập nhật code</t>
+  </si>
+  <si>
+    <t>AI hướng dẫn kiểm tra PID, taskkill và restart server đúng cách.</t>
+  </si>
+  <si>
+    <t>Biết cách xử lý lỗi bind port trong VS Code.</t>
+  </si>
+  <si>
+    <t>Thêm Merge Sort vào endpoint /csv-songs</t>
+  </si>
+  <si>
+    <t>AI hướng dẫn thêm PlaylistSorter.sortByTitle() sau khi filter.</t>
+  </si>
+  <si>
+    <t>AI kiểm tra api.js và kết luận API không có lỗi.</t>
+  </si>
+  <si>
+    <t>AI xác định cổng 8085 đang bị chiếm và hướng dẫn dùng netstat, taskkill.</t>
+  </si>
+  <si>
+    <t>AI yêu cầu in System.out.println() để kiểm tra hàm sortByTitle() có được gọi không.</t>
+  </si>
+  <si>
+    <t>Tìm getCsvSongs()</t>
+  </si>
+  <si>
+    <t>AI yêu cầu kiểm tra file player.js/search.js để xác nhận request /csv-songs.</t>
+  </si>
+  <si>
+    <t>Incorrect Assumption</t>
+  </si>
+  <si>
+    <t>Sau khi thêm code, danh sách vẫn giữ nguyên thứ tự.</t>
+  </si>
+  <si>
+    <t>Chạy chương trình và kiểm tra giao diện.</t>
+  </si>
+  <si>
+    <t>Tiếp tục kiểm tra endpoint và luồng gọi API thay vì chỉ sửa thuật toán.</t>
+  </si>
+  <si>
+    <t>Đối chiếu cấu trúc project và các file JavaScript.</t>
+  </si>
+  <si>
+    <t>Kiểm tra toàn bộ luồng frontend trước khi kết luận.</t>
+  </si>
+  <si>
+    <t>Premature Conclusion</t>
+  </si>
+  <si>
+    <t>So sánh với trạng thái thực tế của project.</t>
+  </si>
+  <si>
+    <t>Yêu cầu xem toàn bộ MainServer.java và kiểm tra endpoint thực tế trước khi kết luận.</t>
+  </si>
+  <si>
+    <t>AI cho rằng chỉ cần thêm Merge Sort vào MainServer là danh sách sẽ được sắp xếp.</t>
+  </si>
+  <si>
+    <t>AI kết luận api.js không phải nguyên nhân.</t>
+  </si>
+  <si>
+    <t>Chưa đủ bằng chứng vì chưa kiểm tra file player.js/search.js nơi gọi getCsvSongs().</t>
+  </si>
+  <si>
+    <t>AI kết luận lỗi nằm ở MainServer chứ không phải PlaylistSorter.</t>
+  </si>
+  <si>
+    <t>Chưa có đủ dữ liệu để khẳng định vì chưa xem toàn bộ MainServer.java.</t>
+  </si>
+  <si>
+    <t>Tối ưu độ phức tạp thời gian, code java, console</t>
+  </si>
+  <si>
+    <t>Dola AI</t>
+  </si>
+  <si>
+    <t>Hỏi nhanh, present, đôi khi code</t>
+  </si>
+  <si>
+    <t>High (40%)</t>
+  </si>
+  <si>
+    <t>Medium (10%)</t>
+  </si>
+  <si>
+    <t>Low (10%)</t>
+  </si>
+  <si>
+    <t>Hiểu code</t>
   </si>
 </sst>
 </file>
@@ -918,7 +1143,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -991,13 +1216,6 @@
       <i/>
       <sz val="12"/>
       <color rgb="FF666666"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -1133,7 +1351,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1167,29 +1385,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1200,25 +1401,16 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1226,6 +1418,35 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1529,7 +1750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1540,14 +1761,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -1595,165 +1816,179 @@
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C10" t="s">
-        <v>12</v>
+      <c r="C10">
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="4">
         <f>C11/C10</f>
-        <v>0.66666666666666663</v>
+        <v>0.19480519480519481</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="D16" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>25</v>
-      </c>
       <c r="C17" s="7" t="s">
-        <v>26</v>
+        <v>359</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>27</v>
+        <v>356</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>30</v>
+        <v>360</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>34</v>
+        <v>361</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-    </row>
-    <row r="22" spans="1:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>40</v>
+        <v>357</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+    </row>
+    <row r="23" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="8">
-        <v>8</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>42</v>
+      <c r="A24" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B25" s="8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B26" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B27" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>42</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="8">
+        <v>4</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1766,742 +2001,1060 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8" style="21" customWidth="1"/>
-    <col min="2" max="3" width="18" style="21" customWidth="1"/>
-    <col min="4" max="4" width="25" style="21" customWidth="1"/>
-    <col min="5" max="5" width="30" style="21" customWidth="1"/>
-    <col min="6" max="6" width="35" style="21" customWidth="1"/>
-    <col min="7" max="7" width="50" style="21" customWidth="1"/>
-    <col min="8" max="8" width="20" style="21" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="21"/>
+    <col min="1" max="1" width="8" style="17" customWidth="1"/>
+    <col min="2" max="3" width="18" style="17" customWidth="1"/>
+    <col min="4" max="4" width="25" style="17" customWidth="1"/>
+    <col min="5" max="5" width="30" style="17" customWidth="1"/>
+    <col min="6" max="6" width="35" style="17" customWidth="1"/>
+    <col min="7" max="7" width="50" style="17" customWidth="1"/>
+    <col min="8" max="8" width="20" style="17" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+    </row>
+    <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+    </row>
+    <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-    </row>
-    <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="E3" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-    </row>
-    <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="24" t="s">
+      <c r="F3" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="G3" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="H3" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="24" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="19">
+        <v>1</v>
+      </c>
+      <c r="B4" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="C4" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="E4" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="F4" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="G4" s="19" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="25">
-        <v>1</v>
-      </c>
-      <c r="B4" s="25" t="s">
+      <c r="H4" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="25" t="s">
+    </row>
+    <row r="5" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="19">
+        <v>2</v>
+      </c>
+      <c r="B5" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="C5" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="E5" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="G4" s="25" t="s">
+      <c r="F5" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="H4" s="25" t="s">
+      <c r="G5" s="19" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25">
-        <v>2</v>
-      </c>
-      <c r="B5" s="25" t="s">
+      <c r="H5" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="25" t="s">
+    </row>
+    <row r="6" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="19">
+        <v>3</v>
+      </c>
+      <c r="B6" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="C6" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="E6" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="F6" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="25" t="s">
+      <c r="G6" s="19" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25">
-        <v>3</v>
-      </c>
-      <c r="B6" s="25" t="s">
+      <c r="H6" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="H6" s="25" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="7" spans="1:8" ht="132" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25">
+      <c r="A7" s="19">
         <v>4</v>
       </c>
-      <c r="B7" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="E7" s="25" t="s">
+      <c r="B7" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="109.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="19">
+        <v>5</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="D8" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="E8" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="F8" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="H7" s="25" t="s">
+      <c r="G8" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="H8" s="19" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="109.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="25">
-        <v>5</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="25" t="s">
+    <row r="9" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="19">
+        <v>6</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="32">
+        <v>7</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="H10" s="32" t="s">
         <v>152</v>
       </c>
-      <c r="D8" s="25" t="s">
-        <v>143</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>144</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="G8" s="25" t="s">
+    </row>
+    <row r="11" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="32"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="H11" s="32"/>
+    </row>
+    <row r="12" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="32">
+        <v>8</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="H8" s="25" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="25">
-        <v>6</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="F9" s="25" t="s">
+      <c r="D12" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="H12" s="32" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="32"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="H13" s="32"/>
+    </row>
+    <row r="14" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="32">
+        <v>9</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="E14" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="F14" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="H14" s="32" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="32"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="H15" s="32"/>
+    </row>
+    <row r="16" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="32">
+        <v>10</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="E16" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="H16" s="32" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="32"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="H17" s="32"/>
+    </row>
+    <row r="18" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="32">
+        <v>11</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="E18" s="32" t="s">
+        <v>164</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="H18" s="32" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="32"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="H19" s="32"/>
+    </row>
+    <row r="20" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="32">
+        <v>12</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="D20" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="E20" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="H20" s="32" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="32"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="H21" s="32"/>
+    </row>
+    <row r="22" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="32">
+        <v>13</v>
+      </c>
+      <c r="B22" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="G9" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="H9" s="25" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="26">
-        <v>7</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="F10" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="G10" s="27" t="s">
-        <v>217</v>
-      </c>
-      <c r="H10" s="26" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="26"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="H11" s="26"/>
-    </row>
-    <row r="12" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="26">
-        <v>8</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="G12" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="H12" s="26" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="26"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="27" t="s">
-        <v>220</v>
-      </c>
-      <c r="H13" s="26"/>
-    </row>
-    <row r="14" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="26">
-        <v>9</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="E14" s="26" t="s">
+      <c r="D22" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="E22" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="F22" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="H22" s="32" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="32"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="H23" s="32"/>
+    </row>
+    <row r="24" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="32">
+        <v>14</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="D24" s="32" t="s">
+        <v>173</v>
+      </c>
+      <c r="E24" s="32" t="s">
         <v>200</v>
       </c>
-      <c r="F14" s="26" t="s">
+      <c r="F24" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="G14" s="27" t="s">
-        <v>221</v>
-      </c>
-      <c r="H14" s="26" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="26"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="27" t="s">
-        <v>222</v>
-      </c>
-      <c r="H15" s="26"/>
-    </row>
-    <row r="16" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="26">
-        <v>10</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>165</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="F16" s="26" t="s">
+      <c r="G24" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="H24" s="32" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="32"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="H25" s="32"/>
+    </row>
+    <row r="26" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="32">
+        <v>15</v>
+      </c>
+      <c r="B26" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="E26" s="32" t="s">
         <v>202</v>
       </c>
-      <c r="G16" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="H16" s="26" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="26"/>
-      <c r="B17" s="26"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="27" t="s">
-        <v>224</v>
-      </c>
-      <c r="H17" s="26"/>
-    </row>
-    <row r="18" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="26">
-        <v>11</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>168</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>170</v>
-      </c>
-      <c r="G18" s="27" t="s">
-        <v>225</v>
-      </c>
-      <c r="H18" s="26" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="26"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="27" t="s">
-        <v>226</v>
-      </c>
-      <c r="H19" s="26"/>
-    </row>
-    <row r="20" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="26">
-        <v>12</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>172</v>
-      </c>
-      <c r="E20" s="26" t="s">
+      <c r="F26" s="32" t="s">
+        <v>177</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="H26" s="32" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="32"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="H27" s="32"/>
+    </row>
+    <row r="28" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="20">
+        <v>16</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="D28" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="F20" s="26" t="s">
+      <c r="E28" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="G20" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="H20" s="26" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="26"/>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="27" t="s">
-        <v>228</v>
-      </c>
-      <c r="H21" s="26"/>
-    </row>
-    <row r="22" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="26">
-        <v>13</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="F22" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="G22" s="27" t="s">
-        <v>229</v>
-      </c>
-      <c r="H22" s="26" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="26"/>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="27" t="s">
+      <c r="F28" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="G28" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="H23" s="26"/>
-    </row>
-    <row r="24" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="26">
-        <v>14</v>
-      </c>
-      <c r="B24" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="D24" s="26" t="s">
+      <c r="H28" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="E24" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="F24" s="26" t="s">
+    </row>
+    <row r="29" spans="1:8" ht="78" x14ac:dyDescent="0.3">
+      <c r="A29" s="32">
+        <v>17</v>
+      </c>
+      <c r="B29" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>180</v>
+      </c>
+      <c r="E29" s="32" t="s">
         <v>206</v>
       </c>
-      <c r="G24" s="27" t="s">
+      <c r="F29" s="32" t="s">
+        <v>207</v>
+      </c>
+      <c r="G29" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="H24" s="26" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="26"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="27" t="s">
+      <c r="H29" s="32" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="32"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="H25" s="26"/>
-    </row>
-    <row r="26" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="26">
-        <v>15</v>
-      </c>
-      <c r="B26" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="26" t="s">
-        <v>180</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="F26" s="26" t="s">
+      <c r="H30" s="32"/>
+    </row>
+    <row r="31" spans="1:8" ht="78" x14ac:dyDescent="0.3">
+      <c r="A31" s="32">
+        <v>18</v>
+      </c>
+      <c r="B31" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="32" t="s">
         <v>182</v>
       </c>
-      <c r="G26" s="27" t="s">
+      <c r="D31" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="E31" s="32" t="s">
+        <v>208</v>
+      </c>
+      <c r="F31" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="G31" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="H26" s="26" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A27" s="26"/>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="27" t="s">
+      <c r="H31" s="32" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="32"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="H27" s="26"/>
-    </row>
-    <row r="28" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="27">
-        <v>16</v>
-      </c>
-      <c r="B28" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="D28" s="27" t="s">
-        <v>208</v>
-      </c>
-      <c r="E28" s="27" t="s">
+      <c r="H32" s="32"/>
+    </row>
+    <row r="33" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="32">
+        <v>19</v>
+      </c>
+      <c r="B33" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="D33" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="E33" s="32" t="s">
         <v>209</v>
       </c>
-      <c r="F28" s="27" t="s">
+      <c r="F33" s="32" t="s">
         <v>210</v>
       </c>
-      <c r="G28" s="27" t="s">
+      <c r="G33" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="H28" s="27" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="78" x14ac:dyDescent="0.3">
-      <c r="A29" s="26">
-        <v>17</v>
-      </c>
-      <c r="B29" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="D29" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="E29" s="26" t="s">
+      <c r="H33" s="32" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="32"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="H34" s="32"/>
+    </row>
+    <row r="35" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="20">
+        <v>20</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="E35" s="20" t="s">
         <v>211</v>
       </c>
-      <c r="F29" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="G29" s="27" t="s">
-        <v>236</v>
-      </c>
-      <c r="H29" s="26" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="26"/>
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="27" t="s">
+      <c r="F35" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="G35" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="H30" s="26"/>
-    </row>
-    <row r="31" spans="1:8" ht="78" x14ac:dyDescent="0.3">
-      <c r="A31" s="26">
-        <v>18</v>
-      </c>
-      <c r="B31" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="D31" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="E31" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="F31" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="G31" s="27" t="s">
-        <v>238</v>
-      </c>
-      <c r="H31" s="26" t="s">
+      <c r="H35" s="20" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="26"/>
-      <c r="B32" s="26"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="27" t="s">
-        <v>239</v>
-      </c>
-      <c r="H32" s="26"/>
-    </row>
-    <row r="33" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="26">
-        <v>19</v>
-      </c>
-      <c r="B33" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C33" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="E33" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="F33" s="26" t="s">
-        <v>215</v>
-      </c>
-      <c r="G33" s="27" t="s">
-        <v>240</v>
-      </c>
-      <c r="H33" s="26" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="26"/>
-      <c r="B34" s="26"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="27" t="s">
-        <v>241</v>
-      </c>
-      <c r="H34" s="26"/>
-    </row>
-    <row r="35" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="27">
-        <v>20</v>
-      </c>
-      <c r="B35" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="C35" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="D35" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="E35" s="27" t="s">
-        <v>216</v>
-      </c>
-      <c r="F35" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="G35" s="27" t="s">
-        <v>242</v>
-      </c>
-      <c r="H35" s="27" t="s">
-        <v>195</v>
+    <row r="36" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="39">
+        <v>21</v>
+      </c>
+      <c r="B36" s="38" t="s">
+        <v>283</v>
+      </c>
+      <c r="C36" s="38" t="s">
+        <v>284</v>
+      </c>
+      <c r="D36" s="38" t="s">
+        <v>285</v>
+      </c>
+      <c r="E36" s="38" t="s">
+        <v>286</v>
+      </c>
+      <c r="F36" s="38" t="s">
+        <v>287</v>
+      </c>
+      <c r="G36" s="38" t="s">
+        <v>288</v>
+      </c>
+      <c r="H36" s="38" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="39">
+        <v>22</v>
+      </c>
+      <c r="B37" s="38" t="s">
+        <v>290</v>
+      </c>
+      <c r="C37" s="38" t="s">
+        <v>284</v>
+      </c>
+      <c r="D37" s="38" t="s">
+        <v>291</v>
+      </c>
+      <c r="E37" s="38" t="s">
+        <v>292</v>
+      </c>
+      <c r="F37" s="38" t="s">
+        <v>293</v>
+      </c>
+      <c r="G37" s="38" t="s">
+        <v>294</v>
+      </c>
+      <c r="H37" s="38" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A38" s="39">
+        <v>23</v>
+      </c>
+      <c r="B38" s="38" t="s">
+        <v>295</v>
+      </c>
+      <c r="C38" s="38" t="s">
+        <v>296</v>
+      </c>
+      <c r="D38" s="38" t="s">
+        <v>297</v>
+      </c>
+      <c r="E38" s="38" t="s">
+        <v>298</v>
+      </c>
+      <c r="F38" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="G38" s="38" t="s">
+        <v>300</v>
+      </c>
+      <c r="H38" s="38" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="39">
+        <v>24</v>
+      </c>
+      <c r="B39" s="38" t="s">
+        <v>302</v>
+      </c>
+      <c r="C39" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="D39" s="38" t="s">
+        <v>335</v>
+      </c>
+      <c r="E39" s="38" t="s">
+        <v>304</v>
+      </c>
+      <c r="F39" s="38" t="s">
+        <v>336</v>
+      </c>
+      <c r="G39" s="38" t="s">
+        <v>305</v>
+      </c>
+      <c r="H39" s="38" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A40" s="39">
+        <v>25</v>
+      </c>
+      <c r="B40" s="38" t="s">
+        <v>302</v>
+      </c>
+      <c r="C40" s="38" t="s">
+        <v>307</v>
+      </c>
+      <c r="D40" s="38" t="s">
+        <v>308</v>
+      </c>
+      <c r="E40" s="38" t="s">
+        <v>309</v>
+      </c>
+      <c r="F40" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="G40" s="38" t="s">
+        <v>310</v>
+      </c>
+      <c r="H40" s="38" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A41" s="39">
+        <v>26</v>
+      </c>
+      <c r="B41" s="38" t="s">
+        <v>302</v>
+      </c>
+      <c r="C41" s="38" t="s">
+        <v>312</v>
+      </c>
+      <c r="D41" s="38" t="s">
+        <v>313</v>
+      </c>
+      <c r="E41" s="38" t="s">
+        <v>314</v>
+      </c>
+      <c r="F41" s="38" t="s">
+        <v>338</v>
+      </c>
+      <c r="G41" s="38" t="s">
+        <v>315</v>
+      </c>
+      <c r="H41" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="39">
+        <v>27</v>
+      </c>
+      <c r="B42" s="38" t="s">
+        <v>317</v>
+      </c>
+      <c r="C42" s="38" t="s">
+        <v>312</v>
+      </c>
+      <c r="D42" s="38" t="s">
+        <v>318</v>
+      </c>
+      <c r="E42" s="38" t="s">
+        <v>319</v>
+      </c>
+      <c r="F42" s="38" t="s">
+        <v>339</v>
+      </c>
+      <c r="G42" s="38" t="s">
+        <v>320</v>
+      </c>
+      <c r="H42" s="38" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="39">
+        <v>28</v>
+      </c>
+      <c r="B43" s="38" t="s">
+        <v>321</v>
+      </c>
+      <c r="C43" s="38" t="s">
+        <v>322</v>
+      </c>
+      <c r="D43" s="38" t="s">
+        <v>323</v>
+      </c>
+      <c r="E43" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="F43" s="38" t="s">
+        <v>341</v>
+      </c>
+      <c r="G43" s="38" t="s">
+        <v>324</v>
+      </c>
+      <c r="H43" s="38" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A44" s="39">
+        <v>29</v>
+      </c>
+      <c r="B44" s="38" t="s">
+        <v>325</v>
+      </c>
+      <c r="C44" s="38" t="s">
+        <v>302</v>
+      </c>
+      <c r="D44" s="38" t="s">
+        <v>326</v>
+      </c>
+      <c r="E44" s="38" t="s">
+        <v>327</v>
+      </c>
+      <c r="F44" s="38" t="s">
+        <v>328</v>
+      </c>
+      <c r="G44" s="38" t="s">
+        <v>329</v>
+      </c>
+      <c r="H44" s="38" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A45" s="39">
+        <v>30</v>
+      </c>
+      <c r="B45" s="38" t="s">
+        <v>330</v>
+      </c>
+      <c r="C45" s="38" t="s">
+        <v>312</v>
+      </c>
+      <c r="D45" s="38" t="s">
+        <v>331</v>
+      </c>
+      <c r="E45" s="38" t="s">
+        <v>332</v>
+      </c>
+      <c r="F45" s="38" t="s">
+        <v>333</v>
+      </c>
+      <c r="G45" s="38" t="s">
+        <v>334</v>
+      </c>
+      <c r="H45" s="38" t="s">
+        <v>316</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="86">
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
     <mergeCell ref="F29:F30"/>
     <mergeCell ref="H29:H30"/>
     <mergeCell ref="A31:A32"/>
@@ -2516,71 +3069,13 @@
     <mergeCell ref="C29:C30"/>
     <mergeCell ref="D29:D30"/>
     <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2597,256 +3092,292 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+    </row>
+    <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-    </row>
-    <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="E3" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-    </row>
-    <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="32" t="s">
+      <c r="F3" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="32" t="s">
+    </row>
+    <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="22">
+        <v>3</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C4" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D4" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E4" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="F4" s="22" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="29">
-        <v>3</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="F4" s="29" t="s">
-        <v>86</v>
-      </c>
-    </row>
     <row r="5" spans="1:6" ht="93.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="29">
+      <c r="A5" s="22">
         <v>5</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="22">
+        <v>6</v>
+      </c>
+      <c r="B6" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C6" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D6" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E6" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F6" s="22" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="29">
-        <v>6</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>148</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>151</v>
-      </c>
-    </row>
     <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="33">
+      <c r="A7" s="20">
         <v>7</v>
       </c>
-      <c r="B7" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="27" t="s">
+      <c r="B7" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="20">
+        <v>8</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="F8" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="D7" s="27" t="s">
+    </row>
+    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="20">
+        <v>9</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="20">
+        <v>13</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="E7" s="27" t="s">
-        <v>255</v>
-      </c>
-      <c r="F7" s="27" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="33">
-        <v>8</v>
-      </c>
-      <c r="B8" s="27" t="s">
+      <c r="D10" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="C8" s="27" t="s">
-        <v>257</v>
-      </c>
-      <c r="D8" s="27" t="s">
+      <c r="E10" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="20">
+        <v>17</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="E8" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="F8" s="27" t="s">
+      <c r="D11" s="20" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="33">
-        <v>9</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>246</v>
-      </c>
-      <c r="C9" s="27" t="s">
+      <c r="E11" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="F11" s="20" t="s">
         <v>260</v>
       </c>
-      <c r="D9" s="27" t="s">
-        <v>247</v>
-      </c>
-      <c r="E9" s="27" t="s">
+    </row>
+    <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="20">
+        <v>22</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="D12" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="E12" s="20" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="33">
-        <v>13</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>248</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>249</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>250</v>
-      </c>
-      <c r="F10" s="27" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="33">
-        <v>17</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" s="27" t="s">
+      <c r="F12" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="D11" s="27" t="s">
-        <v>264</v>
-      </c>
-      <c r="E11" s="27" t="s">
-        <v>252</v>
-      </c>
-      <c r="F11" s="27" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="33">
-        <v>22</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>266</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>267</v>
-      </c>
-      <c r="F12" s="27" t="s">
-        <v>268</v>
-      </c>
     </row>
     <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="28"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
+      <c r="A13" s="39">
+        <v>24</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>342</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>351</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>343</v>
+      </c>
+      <c r="E13" s="38" t="s">
+        <v>344</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="A14" s="39">
+        <v>25</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>342</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>352</v>
+      </c>
+      <c r="D14" s="38" t="s">
+        <v>353</v>
+      </c>
+      <c r="E14" s="38" t="s">
+        <v>346</v>
+      </c>
+      <c r="F14" s="38" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="A15" s="39">
+        <v>29</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>348</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>354</v>
+      </c>
+      <c r="D15" s="38" t="s">
+        <v>355</v>
+      </c>
+      <c r="E15" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="16" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="A16" s="21"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
     </row>
     <row r="17" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
@@ -2914,73 +3445,73 @@
     </row>
     <row r="30" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2989,6 +3520,7 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3004,278 +3536,278 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
+      <c r="A1" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
+      <c r="A2" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>270</v>
+        <v>109</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C8" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="D8" s="34" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>119</v>
-      </c>
       <c r="C9" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D10" s="34" t="s">
-        <v>273</v>
+        <v>109</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D14" s="34" t="s">
-        <v>274</v>
+        <v>109</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D17" s="34" t="s">
-        <v>277</v>
+        <v>109</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D18" s="34" t="s">
-        <v>278</v>
+        <v>109</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A27" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="38" t="s">
-        <v>134</v>
-      </c>
-      <c r="C27" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="D27" s="38" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="156" x14ac:dyDescent="0.3">
-      <c r="A28" s="35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="25">
         <v>1</v>
       </c>
-      <c r="B28" s="36" t="s">
+      <c r="B28" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="C28" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="25">
+        <v>2</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="C29" s="26" t="s">
+        <v>279</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="78" x14ac:dyDescent="0.3">
+      <c r="A30" s="25">
+        <v>3</v>
+      </c>
+      <c r="B30" s="26" t="s">
         <v>281</v>
       </c>
-      <c r="C28" s="36" t="s">
-        <v>279</v>
-      </c>
-      <c r="D28" s="36" t="s">
+      <c r="C30" s="26" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" ht="93.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="35">
-        <v>2</v>
-      </c>
-      <c r="B29" s="36" t="s">
-        <v>283</v>
-      </c>
-      <c r="C29" s="36" t="s">
-        <v>284</v>
-      </c>
-      <c r="D29" s="36" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="78" x14ac:dyDescent="0.3">
-      <c r="A30" s="35">
-        <v>3</v>
-      </c>
-      <c r="B30" s="36" t="s">
-        <v>286</v>
-      </c>
-      <c r="C30" s="36" t="s">
-        <v>287</v>
-      </c>
-      <c r="D30" s="36" t="s">
-        <v>280</v>
+      <c r="D30" s="26" t="s">
+        <v>275</v>
       </c>
     </row>
   </sheetData>

--- a/Ai log/AI_AuditLog_Nghia.xlsx
+++ b/Ai log/AI_AuditLog_Nghia.xlsx
@@ -1419,16 +1419,16 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1436,17 +1436,17 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1761,14 +1761,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -2221,346 +2221,346 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="32">
+      <c r="A10" s="36">
         <v>7</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="36" t="s">
         <v>191</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="36" t="s">
         <v>192</v>
       </c>
       <c r="G10" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="H10" s="32" t="s">
+      <c r="H10" s="36" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="32"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
+      <c r="A11" s="36"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
       <c r="G11" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="H11" s="32"/>
+      <c r="H11" s="36"/>
     </row>
     <row r="12" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="32">
+      <c r="A12" s="36">
         <v>8</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="36" t="s">
         <v>193</v>
       </c>
-      <c r="F12" s="32" t="s">
+      <c r="F12" s="36" t="s">
         <v>194</v>
       </c>
       <c r="G12" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="H12" s="32" t="s">
+      <c r="H12" s="36" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="32"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
+      <c r="A13" s="36"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
       <c r="G13" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="H13" s="32"/>
+      <c r="H13" s="36"/>
     </row>
     <row r="14" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="32">
+      <c r="A14" s="36">
         <v>9</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="36" t="s">
         <v>195</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="F14" s="36" t="s">
         <v>196</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="H14" s="32" t="s">
+      <c r="H14" s="36" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="32"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
+      <c r="A15" s="36"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
       <c r="G15" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="H15" s="32"/>
+      <c r="H15" s="36"/>
     </row>
     <row r="16" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="32">
+      <c r="A16" s="36">
         <v>10</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="36" t="s">
         <v>160</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="36" t="s">
         <v>161</v>
       </c>
-      <c r="F16" s="32" t="s">
+      <c r="F16" s="36" t="s">
         <v>197</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="H16" s="32" t="s">
+      <c r="H16" s="36" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="32"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
+      <c r="A17" s="36"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
       <c r="G17" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="H17" s="32"/>
+      <c r="H17" s="36"/>
     </row>
     <row r="18" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="32">
+      <c r="A18" s="36">
         <v>11</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="36" t="s">
         <v>163</v>
       </c>
-      <c r="E18" s="32" t="s">
+      <c r="E18" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="F18" s="32" t="s">
+      <c r="F18" s="36" t="s">
         <v>165</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="H18" s="32" t="s">
+      <c r="H18" s="36" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="32"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
+      <c r="A19" s="36"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
       <c r="G19" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="H19" s="32"/>
+      <c r="H19" s="36"/>
     </row>
     <row r="20" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="32">
+      <c r="A20" s="36">
         <v>12</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="E20" s="32" t="s">
+      <c r="E20" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="F20" s="32" t="s">
+      <c r="F20" s="36" t="s">
         <v>199</v>
       </c>
       <c r="G20" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="H20" s="32" t="s">
+      <c r="H20" s="36" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="32"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
+      <c r="A21" s="36"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
       <c r="G21" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="H21" s="32"/>
+      <c r="H21" s="36"/>
     </row>
     <row r="22" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="32">
+      <c r="A22" s="36">
         <v>13</v>
       </c>
-      <c r="B22" s="32" t="s">
+      <c r="B22" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="32" t="s">
+      <c r="C22" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D22" s="36" t="s">
         <v>169</v>
       </c>
-      <c r="E22" s="32" t="s">
+      <c r="E22" s="36" t="s">
         <v>170</v>
       </c>
-      <c r="F22" s="32" t="s">
+      <c r="F22" s="36" t="s">
         <v>171</v>
       </c>
       <c r="G22" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="H22" s="32" t="s">
+      <c r="H22" s="36" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="32"/>
-      <c r="B23" s="32"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
+      <c r="A23" s="36"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
       <c r="G23" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="H23" s="32"/>
+      <c r="H23" s="36"/>
     </row>
     <row r="24" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="32">
+      <c r="A24" s="36">
         <v>14</v>
       </c>
-      <c r="B24" s="32" t="s">
+      <c r="B24" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="C24" s="32" t="s">
+      <c r="C24" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="36" t="s">
         <v>173</v>
       </c>
-      <c r="E24" s="32" t="s">
+      <c r="E24" s="36" t="s">
         <v>200</v>
       </c>
-      <c r="F24" s="32" t="s">
+      <c r="F24" s="36" t="s">
         <v>201</v>
       </c>
       <c r="G24" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="H24" s="32" t="s">
+      <c r="H24" s="36" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="32"/>
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
+      <c r="A25" s="36"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="36"/>
       <c r="G25" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="H25" s="32"/>
+      <c r="H25" s="36"/>
     </row>
     <row r="26" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="32">
+      <c r="A26" s="36">
         <v>15</v>
       </c>
-      <c r="B26" s="32" t="s">
+      <c r="B26" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="C26" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="D26" s="32" t="s">
+      <c r="D26" s="36" t="s">
         <v>176</v>
       </c>
-      <c r="E26" s="32" t="s">
+      <c r="E26" s="36" t="s">
         <v>202</v>
       </c>
-      <c r="F26" s="32" t="s">
+      <c r="F26" s="36" t="s">
         <v>177</v>
       </c>
       <c r="G26" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="H26" s="32" t="s">
+      <c r="H26" s="36" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A27" s="32"/>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
+      <c r="A27" s="36"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
       <c r="G27" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="H27" s="32"/>
+      <c r="H27" s="36"/>
     </row>
     <row r="28" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A28" s="20">
@@ -2589,118 +2589,118 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="78" x14ac:dyDescent="0.3">
-      <c r="A29" s="32">
+      <c r="A29" s="36">
         <v>17</v>
       </c>
-      <c r="B29" s="32" t="s">
+      <c r="B29" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="C29" s="32" t="s">
+      <c r="C29" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="D29" s="32" t="s">
+      <c r="D29" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="E29" s="32" t="s">
+      <c r="E29" s="36" t="s">
         <v>206</v>
       </c>
-      <c r="F29" s="32" t="s">
+      <c r="F29" s="36" t="s">
         <v>207</v>
       </c>
       <c r="G29" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="H29" s="32" t="s">
+      <c r="H29" s="36" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="32"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
+      <c r="A30" s="36"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
       <c r="G30" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="H30" s="32"/>
+      <c r="H30" s="36"/>
     </row>
     <row r="31" spans="1:8" ht="78" x14ac:dyDescent="0.3">
-      <c r="A31" s="32">
+      <c r="A31" s="36">
         <v>18</v>
       </c>
-      <c r="B31" s="32" t="s">
+      <c r="B31" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="C31" s="32" t="s">
+      <c r="C31" s="36" t="s">
         <v>182</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="D31" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="E31" s="32" t="s">
+      <c r="E31" s="36" t="s">
         <v>208</v>
       </c>
-      <c r="F31" s="32" t="s">
+      <c r="F31" s="36" t="s">
         <v>184</v>
       </c>
       <c r="G31" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="H31" s="32" t="s">
+      <c r="H31" s="36" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="32"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="32"/>
+      <c r="A32" s="36"/>
+      <c r="B32" s="36"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="36"/>
       <c r="G32" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="H32" s="32"/>
+      <c r="H32" s="36"/>
     </row>
     <row r="33" spans="1:8" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="32">
+      <c r="A33" s="36">
         <v>19</v>
       </c>
-      <c r="B33" s="32" t="s">
+      <c r="B33" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="C33" s="32" t="s">
+      <c r="C33" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="E33" s="32" t="s">
+      <c r="E33" s="36" t="s">
         <v>209</v>
       </c>
-      <c r="F33" s="32" t="s">
+      <c r="F33" s="36" t="s">
         <v>210</v>
       </c>
       <c r="G33" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="H33" s="32" t="s">
+      <c r="H33" s="36" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="32"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32"/>
+      <c r="A34" s="36"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
       <c r="G34" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="H34" s="32"/>
+      <c r="H34" s="36"/>
     </row>
     <row r="35" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="20">
@@ -2729,276 +2729,330 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="39">
+      <c r="A36" s="30">
         <v>21</v>
       </c>
-      <c r="B36" s="38" t="s">
+      <c r="B36" s="29" t="s">
         <v>283</v>
       </c>
-      <c r="C36" s="38" t="s">
+      <c r="C36" s="29" t="s">
         <v>284</v>
       </c>
-      <c r="D36" s="38" t="s">
+      <c r="D36" s="29" t="s">
         <v>285</v>
       </c>
-      <c r="E36" s="38" t="s">
+      <c r="E36" s="29" t="s">
         <v>286</v>
       </c>
-      <c r="F36" s="38" t="s">
+      <c r="F36" s="29" t="s">
         <v>287</v>
       </c>
-      <c r="G36" s="38" t="s">
+      <c r="G36" s="29" t="s">
         <v>288</v>
       </c>
-      <c r="H36" s="38" t="s">
+      <c r="H36" s="29" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="39">
+      <c r="A37" s="30">
         <v>22</v>
       </c>
-      <c r="B37" s="38" t="s">
+      <c r="B37" s="29" t="s">
         <v>290</v>
       </c>
-      <c r="C37" s="38" t="s">
+      <c r="C37" s="29" t="s">
         <v>284</v>
       </c>
-      <c r="D37" s="38" t="s">
+      <c r="D37" s="29" t="s">
         <v>291</v>
       </c>
-      <c r="E37" s="38" t="s">
+      <c r="E37" s="29" t="s">
         <v>292</v>
       </c>
-      <c r="F37" s="38" t="s">
+      <c r="F37" s="29" t="s">
         <v>293</v>
       </c>
-      <c r="G37" s="38" t="s">
+      <c r="G37" s="29" t="s">
         <v>294</v>
       </c>
-      <c r="H37" s="38" t="s">
+      <c r="H37" s="29" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="39">
+      <c r="A38" s="30">
         <v>23</v>
       </c>
-      <c r="B38" s="38" t="s">
+      <c r="B38" s="29" t="s">
         <v>295</v>
       </c>
-      <c r="C38" s="38" t="s">
+      <c r="C38" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="D38" s="38" t="s">
+      <c r="D38" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="E38" s="38" t="s">
+      <c r="E38" s="29" t="s">
         <v>298</v>
       </c>
-      <c r="F38" s="38" t="s">
+      <c r="F38" s="29" t="s">
         <v>299</v>
       </c>
-      <c r="G38" s="38" t="s">
+      <c r="G38" s="29" t="s">
         <v>300</v>
       </c>
-      <c r="H38" s="38" t="s">
+      <c r="H38" s="29" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="39">
+      <c r="A39" s="30">
         <v>24</v>
       </c>
-      <c r="B39" s="38" t="s">
+      <c r="B39" s="29" t="s">
         <v>302</v>
       </c>
-      <c r="C39" s="38" t="s">
+      <c r="C39" s="29" t="s">
         <v>303</v>
       </c>
-      <c r="D39" s="38" t="s">
+      <c r="D39" s="29" t="s">
         <v>335</v>
       </c>
-      <c r="E39" s="38" t="s">
+      <c r="E39" s="29" t="s">
         <v>304</v>
       </c>
-      <c r="F39" s="38" t="s">
+      <c r="F39" s="29" t="s">
         <v>336</v>
       </c>
-      <c r="G39" s="38" t="s">
+      <c r="G39" s="29" t="s">
         <v>305</v>
       </c>
-      <c r="H39" s="38" t="s">
+      <c r="H39" s="29" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="39">
+      <c r="A40" s="30">
         <v>25</v>
       </c>
-      <c r="B40" s="38" t="s">
+      <c r="B40" s="29" t="s">
         <v>302</v>
       </c>
-      <c r="C40" s="38" t="s">
+      <c r="C40" s="29" t="s">
         <v>307</v>
       </c>
-      <c r="D40" s="38" t="s">
+      <c r="D40" s="29" t="s">
         <v>308</v>
       </c>
-      <c r="E40" s="38" t="s">
+      <c r="E40" s="29" t="s">
         <v>309</v>
       </c>
-      <c r="F40" s="38" t="s">
+      <c r="F40" s="29" t="s">
         <v>337</v>
       </c>
-      <c r="G40" s="38" t="s">
+      <c r="G40" s="29" t="s">
         <v>310</v>
       </c>
-      <c r="H40" s="38" t="s">
+      <c r="H40" s="29" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A41" s="39">
+      <c r="A41" s="30">
         <v>26</v>
       </c>
-      <c r="B41" s="38" t="s">
+      <c r="B41" s="29" t="s">
         <v>302</v>
       </c>
-      <c r="C41" s="38" t="s">
+      <c r="C41" s="29" t="s">
         <v>312</v>
       </c>
-      <c r="D41" s="38" t="s">
+      <c r="D41" s="29" t="s">
         <v>313</v>
       </c>
-      <c r="E41" s="38" t="s">
+      <c r="E41" s="29" t="s">
         <v>314</v>
       </c>
-      <c r="F41" s="38" t="s">
+      <c r="F41" s="29" t="s">
         <v>338</v>
       </c>
-      <c r="G41" s="38" t="s">
+      <c r="G41" s="29" t="s">
         <v>315</v>
       </c>
-      <c r="H41" s="38" t="s">
+      <c r="H41" s="29" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A42" s="39">
+      <c r="A42" s="30">
         <v>27</v>
       </c>
-      <c r="B42" s="38" t="s">
+      <c r="B42" s="29" t="s">
         <v>317</v>
       </c>
-      <c r="C42" s="38" t="s">
+      <c r="C42" s="29" t="s">
         <v>312</v>
       </c>
-      <c r="D42" s="38" t="s">
+      <c r="D42" s="29" t="s">
         <v>318</v>
       </c>
-      <c r="E42" s="38" t="s">
+      <c r="E42" s="29" t="s">
         <v>319</v>
       </c>
-      <c r="F42" s="38" t="s">
+      <c r="F42" s="29" t="s">
         <v>339</v>
       </c>
-      <c r="G42" s="38" t="s">
+      <c r="G42" s="29" t="s">
         <v>320</v>
       </c>
-      <c r="H42" s="38" t="s">
+      <c r="H42" s="29" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="39">
+      <c r="A43" s="30">
         <v>28</v>
       </c>
-      <c r="B43" s="38" t="s">
+      <c r="B43" s="29" t="s">
         <v>321</v>
       </c>
-      <c r="C43" s="38" t="s">
+      <c r="C43" s="29" t="s">
         <v>322</v>
       </c>
-      <c r="D43" s="38" t="s">
+      <c r="D43" s="29" t="s">
         <v>323</v>
       </c>
-      <c r="E43" s="38" t="s">
+      <c r="E43" s="29" t="s">
         <v>340</v>
       </c>
-      <c r="F43" s="38" t="s">
+      <c r="F43" s="29" t="s">
         <v>341</v>
       </c>
-      <c r="G43" s="38" t="s">
+      <c r="G43" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="H43" s="38" t="s">
+      <c r="H43" s="29" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A44" s="39">
+      <c r="A44" s="30">
         <v>29</v>
       </c>
-      <c r="B44" s="38" t="s">
+      <c r="B44" s="29" t="s">
         <v>325</v>
       </c>
-      <c r="C44" s="38" t="s">
+      <c r="C44" s="29" t="s">
         <v>302</v>
       </c>
-      <c r="D44" s="38" t="s">
+      <c r="D44" s="29" t="s">
         <v>326</v>
       </c>
-      <c r="E44" s="38" t="s">
+      <c r="E44" s="29" t="s">
         <v>327</v>
       </c>
-      <c r="F44" s="38" t="s">
+      <c r="F44" s="29" t="s">
         <v>328</v>
       </c>
-      <c r="G44" s="38" t="s">
+      <c r="G44" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="H44" s="38" t="s">
+      <c r="H44" s="29" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A45" s="39">
+      <c r="A45" s="30">
         <v>30</v>
       </c>
-      <c r="B45" s="38" t="s">
+      <c r="B45" s="29" t="s">
         <v>330</v>
       </c>
-      <c r="C45" s="38" t="s">
+      <c r="C45" s="29" t="s">
         <v>312</v>
       </c>
-      <c r="D45" s="38" t="s">
+      <c r="D45" s="29" t="s">
         <v>331</v>
       </c>
-      <c r="E45" s="38" t="s">
+      <c r="E45" s="29" t="s">
         <v>332</v>
       </c>
-      <c r="F45" s="38" t="s">
+      <c r="F45" s="29" t="s">
         <v>333</v>
       </c>
-      <c r="G45" s="38" t="s">
+      <c r="G45" s="29" t="s">
         <v>334</v>
       </c>
-      <c r="H45" s="38" t="s">
+      <c r="H45" s="29" t="s">
         <v>316</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="86">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="H12:H13"/>
     <mergeCell ref="A14:A15"/>
@@ -3013,69 +3067,15 @@
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="D12:D13"/>
     <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="H10:H11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3092,7 +3092,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>69</v>
       </c>
       <c r="B1" s="34"/>
@@ -3102,7 +3102,7 @@
       <c r="F1" s="34"/>
     </row>
     <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="37" t="s">
         <v>70</v>
       </c>
       <c r="B2" s="34"/>
@@ -3312,59 +3312,59 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="39">
+      <c r="A13" s="30">
         <v>24</v>
       </c>
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="29" t="s">
         <v>342</v>
       </c>
-      <c r="C13" s="38" t="s">
+      <c r="C13" s="29" t="s">
         <v>351</v>
       </c>
-      <c r="D13" s="38" t="s">
+      <c r="D13" s="29" t="s">
         <v>343</v>
       </c>
-      <c r="E13" s="38" t="s">
+      <c r="E13" s="29" t="s">
         <v>344</v>
       </c>
-      <c r="F13" s="38" t="s">
+      <c r="F13" s="29" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="39">
+      <c r="A14" s="30">
         <v>25</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="29" t="s">
         <v>342</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="29" t="s">
         <v>352</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="29" t="s">
         <v>353</v>
       </c>
-      <c r="E14" s="38" t="s">
+      <c r="E14" s="29" t="s">
         <v>346</v>
       </c>
-      <c r="F14" s="38" t="s">
+      <c r="F14" s="29" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="39">
+      <c r="A15" s="30">
         <v>29</v>
       </c>
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="29" t="s">
         <v>348</v>
       </c>
-      <c r="C15" s="38" t="s">
+      <c r="C15" s="29" t="s">
         <v>354</v>
       </c>
-      <c r="D15" s="38" t="s">
+      <c r="D15" s="29" t="s">
         <v>355</v>
       </c>
-      <c r="E15" s="38" t="s">
+      <c r="E15" s="29" t="s">
         <v>349</v>
       </c>
       <c r="F15" s="20" t="s">
@@ -3536,20 +3536,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="39" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
